--- a/astro-site/public/dl/guia-dark-kitchen/checklist-equipamiento-obra.xlsx
+++ b/astro-site/public/dl/guia-dark-kitchen/checklist-equipamiento-obra.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist Equipamiento" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Checklist Equipamiento'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -516,7 +518,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -546,6 +548,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -614,7 +617,7 @@
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="7">
         <f>IF(E5=0,"",((F5-E5)/E5))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -644,7 +647,7 @@
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="10">
         <f>IF(E6=0,"",((F6-E6)/E6))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
@@ -674,7 +677,7 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="7">
         <f>IF(E7=0,"",((F7-E7)/E7))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -704,7 +707,7 @@
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="10">
         <f>IF(E8=0,"",((F8-E8)/E8))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
@@ -734,7 +737,7 @@
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="7">
         <f>IF(E9=0,"",((F9-E9)/E9))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -764,7 +767,7 @@
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="10">
         <f>IF(E10=0,"",((F10-E10)/E10))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
@@ -794,7 +797,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="7">
         <f>IF(E11=0,"",((F11-E11)/E11))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
@@ -824,7 +827,7 @@
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="10">
         <f>IF(E12=0,"",((F12-E12)/E12))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
@@ -854,7 +857,7 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="7">
         <f>IF(E13=0,"",((F13-E13)/E13))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -884,7 +887,7 @@
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="10">
         <f>IF(E14=0,"",((F14-E14)/E14))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
@@ -914,7 +917,7 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="7">
         <f>IF(E15=0,"",((F15-E15)/E15))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
@@ -944,7 +947,7 @@
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="10">
         <f>IF(E16=0,"",((F16-E16)/E16))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
@@ -978,7 +981,7 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="7">
         <f>IF(E17=0,"",((F17-E17)/E17))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -1012,7 +1015,7 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="10">
         <f>IF(E18=0,"",((F18-E18)/E18))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
@@ -1046,7 +1049,7 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="7">
         <f>IF(E19=0,"",((F19-E19)/E19))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -1080,7 +1083,7 @@
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="10">
         <f>IF(E20=0,"",((F20-E20)/E20))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
@@ -1114,7 +1117,7 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="7">
         <f>IF(E21=0,"",((F21-E21)/E21))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1148,7 +1151,7 @@
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="10">
         <f>IF(E22=0,"",((F22-E22)/E22))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
@@ -1178,7 +1181,7 @@
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="7">
         <f>IF(E23=0,"",((F23-E23)/E23))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -1212,7 +1215,7 @@
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="10">
         <f>IF(E24=0,"",((F24-E24)/E24))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
@@ -1246,7 +1249,7 @@
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="7">
         <f>IF(E25=0,"",((F25-E25)/E25))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1280,7 +1283,7 @@
       <c r="F26" s="6" t="n"/>
       <c r="G26" s="10">
         <f>IF(E26=0,"",((F26-E26)/E26))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
@@ -1314,7 +1317,7 @@
       <c r="F27" s="6" t="n"/>
       <c r="G27" s="7">
         <f>IF(E27=0,"",((F27-E27)/E27))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -1348,7 +1351,7 @@
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="10">
         <f>IF(E28=0,"",((F28-E28)/E28))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
@@ -1382,7 +1385,7 @@
       <c r="F29" s="6" t="n"/>
       <c r="G29" s="7">
         <f>IF(E29=0,"",((F29-E29)/E29))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -1412,7 +1415,7 @@
       <c r="F30" s="6" t="n"/>
       <c r="G30" s="10">
         <f>IF(E30=0,"",((F30-E30)/E30))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
@@ -1442,7 +1445,7 @@
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="7">
         <f>IF(E31=0,"",((F31-E31)/E31))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -1472,7 +1475,7 @@
       <c r="F32" s="6" t="n"/>
       <c r="G32" s="10">
         <f>IF(E32=0,"",((F32-E32)/E32))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
@@ -1502,7 +1505,7 @@
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="7">
         <f>IF(E33=0,"",((F33-E33)/E33))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -1536,7 +1539,7 @@
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="10">
         <f>IF(E34=0,"",((F34-E34)/E34))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
@@ -1566,7 +1569,7 @@
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="7">
         <f>IF(E35=0,"",((F35-E35)/E35))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -1596,7 +1599,7 @@
       <c r="F36" s="6" t="n"/>
       <c r="G36" s="10">
         <f>IF(E36=0,"",((F36-E36)/E36))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
@@ -1630,7 +1633,7 @@
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="7">
         <f>IF(E37=0,"",((F37-E37)/E37))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
@@ -1660,7 +1663,7 @@
       <c r="F38" s="6" t="n"/>
       <c r="G38" s="10">
         <f>IF(E38=0,"",((F38-E38)/E38))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
@@ -1694,7 +1697,7 @@
       <c r="F39" s="6" t="n"/>
       <c r="G39" s="7">
         <f>IF(E39=0,"",((F39-E39)/E39))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -1724,7 +1727,7 @@
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="10">
         <f>IF(E40=0,"",((F40-E40)/E40))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
@@ -1758,7 +1761,7 @@
       <c r="F41" s="6" t="n"/>
       <c r="G41" s="7">
         <f>IF(E41=0,"",((F41-E41)/E41))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
@@ -1788,7 +1791,7 @@
       <c r="F42" s="6" t="n"/>
       <c r="G42" s="10">
         <f>IF(E42=0,"",((F42-E42)/E42))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
@@ -1818,7 +1821,7 @@
       <c r="F43" s="6" t="n"/>
       <c r="G43" s="7">
         <f>IF(E43=0,"",((F43-E43)/E43))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
@@ -1848,7 +1851,7 @@
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="10">
         <f>IF(E44=0,"",((F44-E44)/E44))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
@@ -1865,15 +1868,15 @@
       </c>
       <c r="E45" s="12">
         <f>SUM(E5:E44)</f>
-        <v/>
+        <v>49550.0</v>
       </c>
       <c r="F45" s="12">
         <f>SUM(F5:F44)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G45" s="13">
         <f>IF(E45=0,"",((F45-E45)/E45))</f>
-        <v/>
+        <v>-1.0</v>
       </c>
     </row>
   </sheetData>
@@ -1886,6 +1889,15 @@
       <formula1>"Pendiente,Pedido,Recibido,Instalado"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>